--- a/Documentos/ProductBacklogCorregido.xlsx
+++ b/Documentos/ProductBacklogCorregido.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveespochedu-my.sharepoint.com/personal/jonathan_aucancela_espoch_edu_ec/Documents/Documentos/Espoch/Octavo/Aplicaciones informáticas 2/Parcial 1/Tareas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{3B73CD9B-AD82-416D-96B8-D24AE7031C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B2ED496-8015-4EDC-AEEC-DC58FE0D766E}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{3B73CD9B-AD82-416D-96B8-D24AE7031C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6FAC07-CC05-4FB7-8775-EA4003927049}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A8F741B-9112-4896-B995-875A9BDE94F9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>Product Backlog - SecuraBank</t>
   </si>
@@ -62,21 +62,12 @@
     <t>2 Gestión de autenticación y acceso</t>
   </si>
   <si>
-    <t>Implementar Control de Acceso Basado en Roles (RBAC)</t>
-  </si>
-  <si>
-    <t>Validar la autenticación con MFA para el acceso de usuarios.</t>
-  </si>
-  <si>
     <t>Establecer reglas de bloqueo por intentos fallidos de inicio de sesión.</t>
   </si>
   <si>
     <t>3 Seguridad en datos y transacciones</t>
   </si>
   <si>
-    <t>Implementar cifrado de datos sensibles usando AES-256.</t>
-  </si>
-  <si>
     <t>Proteger el sistema contra inyección SQL y ataques XSS.</t>
   </si>
   <si>
@@ -215,12 +206,6 @@
     <t>22 de octubre 2024</t>
   </si>
   <si>
-    <t>5 de diciembre 2024</t>
-  </si>
-  <si>
-    <t>26 de diciembre 2024</t>
-  </si>
-  <si>
     <t>HT5</t>
   </si>
   <si>
@@ -236,9 +221,6 @@
     <t>HT7</t>
   </si>
   <si>
-    <t>Crear del prototipo  inicial dl sistema y la base de datos para usuarios y transacciones.</t>
-  </si>
-  <si>
     <t>Configurar el entorno de desarrollo y herramientas necesarias</t>
   </si>
   <si>
@@ -254,7 +236,31 @@
     <t>Diseñar la base de datos inicial y el repositorio del proyecto</t>
   </si>
   <si>
-    <t>12 de diciembre 2024</t>
+    <t>5 de noviembre 2024</t>
+  </si>
+  <si>
+    <t>12 de noviembre 2024</t>
+  </si>
+  <si>
+    <t>26 de noviembre 2024</t>
+  </si>
+  <si>
+    <t>27 de noviembre de2024</t>
+  </si>
+  <si>
+    <t>28 de noviembre de2024</t>
+  </si>
+  <si>
+    <t>30 de noviembre de 2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crear del prototipo  inicial de la base de datos </t>
+  </si>
+  <si>
+    <t>Creacion del esquema según el patrón de diseño.</t>
+  </si>
+  <si>
+    <t>Crear el entorno de desarrollo  Django para el frontend</t>
   </si>
 </sst>
 </file>
@@ -451,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -477,6 +483,24 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -486,23 +510,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,13 +851,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A87B21-3BDC-40F9-B20F-2399C52423D9}">
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="30.33203125" customWidth="1"/>
     <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="7" max="7" width="20.21875" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -873,203 +882,217 @@
         <v>3</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17"/>
+      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C7" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="2">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="2" t="s">
+      <c r="C9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E6" s="2">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="2">
-        <v>4</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="2">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="C11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
         <v>2</v>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="G11" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="2">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1079,33 +1102,33 @@
         <v>4</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E13" s="2">
         <v>4</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
+      <c r="A14" s="9" t="s">
+        <v>16</v>
+      </c>
       <c r="B14" s="2"/>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1120,9 +1143,9 @@
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
+      <c r="A15" s="9"/>
       <c r="B15" s="2"/>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1137,68 +1160,66 @@
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="9"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2">
-        <v>4</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E18" s="2">
         <v>4</v>
       </c>
       <c r="F18" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
+    <row r="19" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="9"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="E19" s="2">
         <v>4</v>
@@ -1208,31 +1229,33 @@
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="12"/>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="B20" s="2"/>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="9"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
@@ -1242,158 +1265,156 @@
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="9"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="2">
+        <v>4</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2">
+        <v>4</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="9"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="9"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="2">
+        <v>4</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="9"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" s="2">
+        <v>4</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="2">
-        <v>4</v>
-      </c>
-      <c r="F22" s="2">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="2">
-        <v>4</v>
-      </c>
-      <c r="F23" s="2">
+      <c r="B28" s="2"/>
+      <c r="C28" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="2">
+        <v>4</v>
+      </c>
+      <c r="F28" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="12"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="2">
-        <v>4</v>
-      </c>
-      <c r="F24" s="2">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="2">
-        <v>4</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E26" s="2">
-        <v>4</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="2">
-        <v>4</v>
-      </c>
-      <c r="F27" s="2">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="1" t="s">
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="9"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="2">
-        <v>4</v>
-      </c>
-      <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="12"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="2">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="9"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E29" s="2">
-        <v>4</v>
-      </c>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="E30" s="2">
         <v>4</v>
@@ -1403,50 +1424,52 @@
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
+    <row r="31" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="9" t="s">
+        <v>44</v>
+      </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="17" t="s">
+      <c r="C31" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="2">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="9"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="2">
-        <v>4</v>
-      </c>
-      <c r="F31" s="2">
-        <v>1</v>
-      </c>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="2">
+        <v>4</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E32" s="2">
-        <v>4</v>
-      </c>
-      <c r="F32" s="2">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E33" s="2">
         <v>4</v>
@@ -1457,32 +1480,30 @@
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="12"/>
+      <c r="A34" s="9"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="9"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E34" s="2">
-        <v>4</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1</v>
-      </c>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B35" s="2"/>
-      <c r="C35" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="E35" s="2">
         <v>4</v>
@@ -1492,51 +1513,51 @@
       </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="12"/>
+    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>46</v>
+      </c>
       <c r="B36" s="2"/>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="14" t="s">
         <v>5</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2"/>
+    </row>
+    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="2">
-        <v>4</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="2">
+        <v>4</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2"/>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E37" s="2">
-        <v>4</v>
-      </c>
-      <c r="F37" s="2">
-        <v>2</v>
-      </c>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A38" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="E38" s="2">
         <v>4</v>
       </c>
@@ -1544,40 +1565,6 @@
         <v>1</v>
       </c>
       <c r="G38" s="2"/>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="2">
-        <v>4</v>
-      </c>
-      <c r="F39" s="2">
-        <v>1</v>
-      </c>
-      <c r="G39" s="2"/>
-    </row>
-    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="2">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2">
-        <v>1</v>
-      </c>
-      <c r="G40" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Documentos/ProductBacklogCorregido.xlsx
+++ b/Documentos/ProductBacklogCorregido.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveespochedu-my.sharepoint.com/personal/jonathan_aucancela_espoch_edu_ec/Documents/Documentos/Espoch/Octavo/Aplicaciones informáticas 2/Parcial 1/Tareas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveespochedu-my.sharepoint.com/personal/jonathan_aucancela_espoch_edu_ec/Documents/Documentos/Espoch/Octavo/Aplicaciones informáticas 2/SGT/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{3B73CD9B-AD82-416D-96B8-D24AE7031C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB6FAC07-CC05-4FB7-8775-EA4003927049}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{3B73CD9B-AD82-416D-96B8-D24AE7031C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCF0C754-8B3A-463B-9238-3F27D86D0877}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{7A8F741B-9112-4896-B995-875A9BDE94F9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Final" sheetId="1" r:id="rId1"/>
+    <sheet name="Historias técnicas" sheetId="2" r:id="rId2"/>
+    <sheet name="Historias de usuarios" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="114">
   <si>
     <t>Product Backlog - SecuraBank</t>
   </si>
@@ -68,12 +70,6 @@
     <t>3 Seguridad en datos y transacciones</t>
   </si>
   <si>
-    <t>Proteger el sistema contra inyección SQL y ataques XSS.</t>
-  </si>
-  <si>
-    <t>Crear pruebas unitarias para validar las medidas de seguridad.</t>
-  </si>
-  <si>
     <t>Desarrollo</t>
   </si>
   <si>
@@ -261,13 +257,156 @@
   </si>
   <si>
     <t>Crear el entorno de desarrollo  Django para el frontend</t>
+  </si>
+  <si>
+    <t>Interfaz de iniciar sesión de la cuenta del usuario.</t>
+  </si>
+  <si>
+    <t>HU3</t>
+  </si>
+  <si>
+    <t>HU4</t>
+  </si>
+  <si>
+    <t>Crear la app usuarios en Django y definir el modelo de usuario personalizado.</t>
+  </si>
+  <si>
+    <t>HT8</t>
+  </si>
+  <si>
+    <t>02 de diciembre de2024</t>
+  </si>
+  <si>
+    <t>Crear la app transacciones y definir el modelo de transacción.</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Criterios de Validación</t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>Definir el perfil y alcance del proyecto.</t>
+  </si>
+  <si>
+    <t>Documento de perfil y alcance aprobado.</t>
+  </si>
+  <si>
+    <t>Realizar un análisis de necesidades, objetivos y metas del proyecto.</t>
+  </si>
+  <si>
+    <t>Configurar el entorno de desarrollo y herramientas necesarias.</t>
+  </si>
+  <si>
+    <t>Todas las herramientas instaladas y configuradas correctamente.</t>
+  </si>
+  <si>
+    <t>Instalar Django, Docker, y configurar entorno virtual.</t>
+  </si>
+  <si>
+    <t>Definir la arquitectura basada en Zero Trust.</t>
+  </si>
+  <si>
+    <t>Esquema de arquitectura revisado y aprobado.</t>
+  </si>
+  <si>
+    <t>Crear diagrama de componentes y flujos de seguridad.</t>
+  </si>
+  <si>
+    <t>Diseñar la base de datos inicial y configurar el repositorio del proyecto.</t>
+  </si>
+  <si>
+    <t>Base de datos funcional y repositorio activo.</t>
+  </si>
+  <si>
+    <t>Crear esquema de base de datos y sincronizar en Git.</t>
+  </si>
+  <si>
+    <t>Prototipo revisado y aprobado por el equipo.</t>
+  </si>
+  <si>
+    <t>Diseñar vistas preliminares y maquetas en Figma o similar.</t>
+  </si>
+  <si>
+    <t>El sistema bloquea al usuario tras X intentos fallidos.</t>
+  </si>
+  <si>
+    <t>Implementar lógica de bloqueo y pruebas unitarias.</t>
+  </si>
+  <si>
+    <t>Crear el esquema según el patrón de diseño seleccionado.</t>
+  </si>
+  <si>
+    <t>Esquema diseñado y documentado correctamente.</t>
+  </si>
+  <si>
+    <t>Implementar el esquema basado en patrón MVC o similar.</t>
+  </si>
+  <si>
+    <t>Crear la app de usuarios en Django y definir el modelo de usuario personalizado.</t>
+  </si>
+  <si>
+    <t>Modelo de usuario funcional con autenticación.</t>
+  </si>
+  <si>
+    <t>Crear el prototipo inicial de la base de datos.</t>
+  </si>
+  <si>
+    <t>Base de datos diseñada y con tablas básicas creadas.</t>
+  </si>
+  <si>
+    <t>Definir las entidades y relaciones, y crear esquema en SQL o Django ORM.</t>
+  </si>
+  <si>
+    <t>Crear el entorno de desarrollo Django para el frontend.</t>
+  </si>
+  <si>
+    <t>Aplicación Django inicializada y funcionando.</t>
+  </si>
+  <si>
+    <t>Crear entorno virtual, iniciar proyecto Django y configuración básica.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extender </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>AbstractUser</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y configurar autenticación personalizada.</t>
+    </r>
+  </si>
+  <si>
+    <t>Interfaces de registro, gestión de transacciones y configuraciones de la cuenta</t>
+  </si>
+  <si>
+    <t>Proceso de componentes para el acceso multifactor y control de acceso.</t>
+  </si>
+  <si>
+    <t>05 de diciembre de 2024</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,8 +444,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,6 +511,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -457,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -486,20 +663,29 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -510,15 +696,17 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF5050"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -851,8 +1039,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83A87B21-3BDC-40F9-B20F-2399C52423D9}">
-  <dimension ref="A1:G38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.77734375" customWidth="1"/>
     <col min="4" max="4" width="30.33203125" customWidth="1"/>
@@ -860,7 +1048,7 @@
     <col min="7" max="7" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30.6" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -871,7 +1059,7 @@
       <c r="F1" s="6"/>
       <c r="G1" s="7"/>
     </row>
-    <row r="2" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="21" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -882,155 +1070,155 @@
         <v>3</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.2" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="39" customHeight="1">
+      <c r="A4" s="19"/>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="45.6" customHeight="1">
+      <c r="A5" s="19"/>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="2">
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" customHeight="1">
+      <c r="A6" s="19"/>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="39" customHeight="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="2">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="C7" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="37.799999999999997" customHeight="1">
+      <c r="A8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="2" t="s">
+      <c r="C8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="2">
-        <v>4</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4</v>
-      </c>
-      <c r="F6" s="2">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="D8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17"/>
-      <c r="B7" s="2" t="s">
+    <row r="9" spans="1:7" ht="43.2" customHeight="1">
+      <c r="A9" s="19"/>
+      <c r="B9" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="2">
-        <v>4</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>50</v>
+      <c r="C9" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
@@ -1042,19 +1230,19 @@
         <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="39.6" customHeight="1">
+      <c r="A10" s="19"/>
       <c r="B10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2">
         <v>4</v>
@@ -1063,19 +1251,19 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="40.200000000000003" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>73</v>
       </c>
       <c r="E11" s="2">
         <v>4</v>
@@ -1084,178 +1272,192 @@
         <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="50.4" customHeight="1">
+      <c r="A12" s="20"/>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="2">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="48.6" customHeight="1">
+      <c r="A13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="14" t="s">
-        <v>5</v>
+      <c r="B13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>48</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" s="2">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="54.6" customHeight="1">
+      <c r="A14" s="19"/>
+      <c r="B14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="2">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="45.6" customHeight="1">
+      <c r="A15" s="19"/>
+      <c r="B15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="2">
+        <v>4</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" ht="51.6" customHeight="1">
+      <c r="A16" s="20"/>
+      <c r="B16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="2">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" ht="51.6" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="2">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="2">
-        <v>4</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="2">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="E17" s="2">
         <v>4</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="28.8">
       <c r="A18" s="9"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2">
         <v>4</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="28.8">
       <c r="A19" s="9"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E19" s="2">
         <v>4</v>
       </c>
       <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" ht="28.8">
+      <c r="A20" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2">
         <v>2</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E20" s="2">
-        <v>4</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="43.2">
       <c r="A21" s="9"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2">
         <v>4</v>
@@ -1265,14 +1467,14 @@
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="31.2" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2">
         <v>4</v>
@@ -1282,16 +1484,16 @@
       </c>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="28.8">
       <c r="A23" s="9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B23" s="2"/>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2">
         <v>4</v>
@@ -1301,50 +1503,50 @@
       </c>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="28.8">
       <c r="A24" s="9"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
         <v>4</v>
       </c>
       <c r="F24" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.2">
       <c r="A25" s="9"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2">
         <v>4</v>
       </c>
       <c r="F25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2"/>
     </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="28.8" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2"/>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E26" s="2">
         <v>4</v>
@@ -1354,14 +1556,14 @@
       </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="43.2">
       <c r="A27" s="9"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="14" t="s">
+      <c r="C27" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E27" s="2">
         <v>4</v>
@@ -1371,33 +1573,33 @@
       </c>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>43</v>
-      </c>
+    <row r="28" spans="1:7" ht="28.8">
+      <c r="A28" s="9"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2">
         <v>4</v>
       </c>
       <c r="F28" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="9"/>
+    <row r="29" spans="1:7" ht="43.2">
+      <c r="A29" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="B29" s="2"/>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E29" s="2">
         <v>4</v>
@@ -1407,33 +1609,33 @@
       </c>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="28.8">
       <c r="A30" s="9"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E30" s="2">
         <v>4</v>
       </c>
       <c r="F30" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="28.8">
       <c r="A31" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B31" s="2"/>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E31" s="2">
         <v>4</v>
@@ -1443,14 +1645,14 @@
       </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="28.8">
       <c r="A32" s="9"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E32" s="2">
         <v>4</v>
@@ -1460,16 +1662,14 @@
       </c>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>45</v>
-      </c>
+    <row r="33" spans="1:7" ht="43.2">
+      <c r="A33" s="9"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E33" s="2">
         <v>4</v>
@@ -1479,67 +1679,69 @@
       </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
+    <row r="34" spans="1:7" ht="57.6">
+      <c r="A34" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="B34" s="2"/>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2">
         <v>4</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="43.2">
       <c r="A35" s="9"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E35" s="2">
         <v>4</v>
       </c>
       <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2"/>
+    </row>
+    <row r="36" spans="1:7" ht="43.2">
+      <c r="A36" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E36" s="2">
+        <v>4</v>
+      </c>
+      <c r="F36" s="2">
         <v>2</v>
       </c>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" s="2">
-        <v>4</v>
-      </c>
-      <c r="F36" s="2">
-        <v>1</v>
-      </c>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="43.2">
       <c r="A37" s="9"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E37" s="2">
         <v>4</v>
@@ -1549,28 +1751,318 @@
       </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="28.8">
       <c r="A38" s="9"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2">
         <v>4</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2"/>
     </row>
+    <row r="39" spans="1:7" ht="28.8">
+      <c r="A39" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="2">
+        <v>4</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2"/>
+    </row>
+    <row r="40" spans="1:7" ht="43.2">
+      <c r="A40" s="9"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="2">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" ht="28.8">
+      <c r="A41" s="9"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="2">
+        <v>4</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A16"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EE2C79-A7B0-4BE1-9026-6C6F59ABCFC9}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="6.77734375" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" customWidth="1"/>
+    <col min="5" max="5" width="37.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="30.6" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="41.4" customHeight="1">
+      <c r="A2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.200000000000003" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="39" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="56.4" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.2" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="37.799999999999997" customHeight="1">
+      <c r="A7" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="40.200000000000003" customHeight="1">
+      <c r="A8" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="54" customHeight="1">
+      <c r="A9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{113AD7C8-E432-4900-8C71-627982E552B0}">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" customWidth="1"/>
+    <col min="5" max="5" width="34.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="32.4" customHeight="1">
+      <c r="A1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="40.799999999999997" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="40.799999999999997" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>